--- a/outputs/loan_form_output.xlsx
+++ b/outputs/loan_form_output.xlsx
@@ -487,11 +487,7 @@
           <t>female</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Name Of (ompany_</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>

--- a/outputs/loan_form_output.xlsx
+++ b/outputs/loan_form_output.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[NOT_SIGNED]</t>
+          <t>[SIGNED]</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">

--- a/outputs/loan_form_output.xlsx
+++ b/outputs/loan_form_output.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,7 +487,11 @@
           <t>female</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Nome of Compony:</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>

--- a/outputs/loan_form_output.xlsx
+++ b/outputs/loan_form_output.xlsx
@@ -479,9 +479,21 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MD. Mahed Hasan</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>01717649301</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>female</t>
